--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556200837</v>
+        <v>46157.93115448968</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115448968</v>
+        <v>46157.93138902533</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93138902533</v>
+        <v>46157.93385679791</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93385679791</v>
+        <v>46157.9369691599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369691599</v>
+        <v>46158.28205758735</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205758735</v>
+        <v>46158.29654261438</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29654261438</v>
+        <v>46158.2980933247</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980933247</v>
+        <v>46158.33371857133</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371857133</v>
+        <v>46158.37223613028</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июль/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37223613028</v>
+        <v>46158.37276372765</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
